--- a/data/sop_data.xlsx
+++ b/data/sop_data.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">DUM39995</t>
   </si>
   <si>
-    <t xml:space="preserve">SOP_AutoTest_15</t>
+    <t xml:space="preserve">SOP_AutoTest_17</t>
   </si>
   <si>
     <t xml:space="preserve">/home/suraksha/Downloads/Correct_Doc.pdf.docx</t>

--- a/data/sop_data.xlsx
+++ b/data/sop_data.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">DUM39995</t>
   </si>
   <si>
-    <t xml:space="preserve">SOP_AutoTest_17</t>
+    <t xml:space="preserve">SOP_AutoTest_18</t>
   </si>
   <si>
     <t xml:space="preserve">/home/suraksha/Downloads/Correct_Doc.pdf.docx</t>

--- a/data/sop_data.xlsx
+++ b/data/sop_data.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">DUM39995</t>
   </si>
   <si>
-    <t xml:space="preserve">SOP_AutoTest_18</t>
+    <t xml:space="preserve">SOP_AutoTest_23</t>
   </si>
   <si>
     <t xml:space="preserve">/home/suraksha/Downloads/Correct_Doc.pdf.docx</t>
